--- a/Общая Тендеры РНД/реестр-лотов-44фз-пешеходные-переходы-видеонаблюдение.xlsx
+++ b/Общая Тендеры РНД/реестр-лотов-44фз-пешеходные-переходы-видеонаблюдение.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Реестр лотов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр лотов'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр лотов'!$A$1:$N$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0158300010126000011</t>
+          <t>0158300033626000068</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -554,43 +554,45 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Администрация Ремонтненского района РО</t>
+          <t>Администрация Сальского городского поселения (ИНН 6153023616)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Замена светофоров Т.7 (с солнечными светильниками) на пешеходных переходах МО дорог</t>
+          <t>Обустройство пешеходных переходов ограждениями и светофорами типа Т-7</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1840797</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>984826</v>
+        <v>1716251</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Контракт заключён 10.08.2026</t>
+          <t>АКТИВНА — приём до 21.08.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0158300010126000011</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0158300033626000068</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0158300010126000011</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0158300033626000068</t>
         </is>
       </c>
     </row>
@@ -610,7 +612,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0358300284526000125</t>
+          <t>0158300010126000011</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -620,43 +622,43 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>МКУ "ДИСОТИ" (дирекция транспортной инфраструктуры г. Ростова-на-Дону)</t>
+          <t>Администрация Ремонтненского района РО</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Капремонт подземного перехода Кировский / Б. Садовая (ОКН, мозаика, видеонаблюдение)</t>
+          <t>Замена светофоров Т.7 (с солнечными светильниками) на пешеходных переходах МО дорог</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>48134495</v>
+        <v>1840797</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46700000</v>
+        <v>984826</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Повторный контракт 07.2026 (~46,7 млн ₽); ранее аукцион 05.2026</t>
+          <t>Контракт заключён 10.08.2026</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>27.05.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300284526000125</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0158300010126000011</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000125</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0158300010126000011</t>
         </is>
       </c>
     </row>
@@ -671,58 +673,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение / фотовидеофиксация</t>
+          <t>Пешеходные переходы</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000003</t>
+          <t>0358300284526000154</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
+          <t>МКУ "ДИСОТИ" (дирекция транспортной инфраструктуры г. Ростова-на-Дону)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Услуги связи (VPN, передача данных с комплексов фиксации нарушений ПДД на территории РО)</t>
+          <t>Переустройство пешеходных переходов на ул. Пушкинской (пер. Доломановский — пр. Театральный)</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10298296</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>10298296</v>
+        <v>8048700</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Контракт с ПАО «МегаФон» 16.02.2026</t>
+          <t>Приём завершён 15.07.2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000003</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0358300284526000154</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000003</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000154</t>
         </is>
       </c>
     </row>
@@ -737,62 +741,58 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение / фотовидеофиксация</t>
+          <t>Пешеходные переходы</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000013</t>
+          <t>0358300284526000125</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Запрос ценовой информации</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
+          <t>МКУ "ДИСОТИ" (дирекция транспортной инфраструктуры г. Ростова-на-Дону)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Гос. метрологическая поверка комплексов фотовидеофиксации нарушений ПДД (61 комплекс)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Капремонт подземного перехода Кировский / Б. Садовая (ОКН, мозаика, видеонаблюдение)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>48134495</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>46700000</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Завершена 04.2026</t>
+          <t>Повторный контракт 07.2026 (~46,7 млн ₽); ранее аукцион 05.2026</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10.04.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zcp20/view/common-info.html?regNumber=0858200000426000013</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300284526000125</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000013</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000125</t>
         </is>
       </c>
     </row>
@@ -807,43 +807,45 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение / фотовидеофиксация</t>
+          <t>Пешеходные переходы</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000014</t>
+          <t>0858300001826000064</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Запрос котировок</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
+          <t>Администрация г. Новошахтинска</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Модернизация комплексов «СКИП-Траффик ПДД» (доп. виды нарушений), 9 комплексов</t>
+          <t>Замена пешеходных светофорных устройств, пер. Водосборный — ул. Советской Конституции</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2655000</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>2655000</v>
+        <v>248333</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Контракт 22.06.2026</t>
+          <t>Завершена 06.2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -853,12 +855,12 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000014</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858300001826000064</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000014</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858300001826000064</t>
         </is>
       </c>
     </row>
@@ -878,7 +880,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000006</t>
+          <t>0858200000426000003</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -893,22 +895,18 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ИБ ГИС «Интеллектуальная транспортная система Ростовской области» (ОКИИ)</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Услуги связи (VPN, передача данных с комплексов фиксации нарушений ПДД на территории РО)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>10298296</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>10298296</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Завершена 04.2026</t>
+          <t>Контракт с ПАО «МегаФон» 16.02.2026</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -918,17 +916,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000006</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000003</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000006</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000003</t>
         </is>
       </c>
     </row>
@@ -948,12 +946,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2616712165226000005</t>
+          <t>0858200000426000015</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -963,38 +961,40 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Поставка электроэнергии для комплексов фиксации</t>
+          <t>VPN и передача данных с комплексов фиксации ПДД в г. Ростов-на-Дону до центрального сервера</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>3500000</v>
+        <v>4533530</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Контракт 04.2026</t>
+          <t>Приём завершён 14.08.2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07.04.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=2616712165226000005</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000015</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=2616712165226000005</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000015</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0358300436226000021</t>
+          <t>0858200000426000016</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1024,43 +1024,45 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
+          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Поставка камер видеонаблюдения цилиндрических, 47 шт.</t>
+          <t>Страхование имущества 71 комплекса фотовидеофиксации нарушений ПДД</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1410000</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1410000</v>
+        <v>1439029</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Завершена 05.2026</t>
+          <t>Приём завершён 18.08.2026</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000021</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000016</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000021</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000016</t>
         </is>
       </c>
     </row>
@@ -1080,55 +1082,53 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0358300436226000022</t>
+          <t>0858200000426000013</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
+          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Мультимедийное ПО системы видеонаблюдения (лицензии)</t>
+          <t>Модернизация 8 комплексов «ЛОБАЧЕВСКИЙ» (доп. виды нарушений ПДД)</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2360000</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>2360000</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Размещена 04.2026</t>
+          <t>Контракт с ИП Батычко 29.05.2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000022</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000013</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000022</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000013</t>
         </is>
       </c>
     </row>
@@ -1138,63 +1138,63 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Россия (федеральные/региональные)</t>
+          <t>Ростовская область</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Пешеходные переходы</t>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000004</t>
+          <t>0858200000426000014</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Открытый конкурс (ЭОК)</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
+          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 659+086, 661+289, 665+613), Чувашия</t>
+          <t>Модернизация комплексов «СКИП-Траффик ПДД» (доп. виды нарушений), 9 комплексов</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>138000000</v>
+        <v>2655000</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>138000000</v>
+        <v>2655000</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Завершена 03.2026; победитель ООО «Вест»</t>
+          <t>Контракт 22.06.2026</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Фабрикант</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>06.03.2026</t>
+          <t>16.06.2026</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000004</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000014</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000004</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000014</t>
         </is>
       </c>
     </row>
@@ -1204,36 +1204,38 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Россия (федеральные/региональные)</t>
+          <t>Ростовская область</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Пешеходные переходы</t>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000003</t>
+          <t>0858200000426000006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Открытый конкурс (ЭОК)</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
+          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 626+954, 632+373, 634+365), Чувашия</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>138000000</v>
+          <t>ИБ ГИС «Интеллектуальная транспортная система Ростовской области» (ОКИИ)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1242,27 +1244,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Завершена 03.2026</t>
+          <t>Завершена 04.2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Фабрикант</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>06.03.2026</t>
+          <t>06.04.2026</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000003</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000006</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000003</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000006</t>
         </is>
       </c>
     </row>
@@ -1272,65 +1274,63 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Россия (федеральные/региональные)</t>
+          <t>Ростовская область</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Пешеходные переходы</t>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000002</t>
+          <t>2616712165226000005</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Открытый конкурс (ЭОК)</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
+          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 622+767, 624+812, 635+693), Чувашия</t>
+          <t>Поставка электроэнергии для комплексов фиксации</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>138000000</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3500000</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3500000</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Завершена 03.2026</t>
+          <t>Контракт 04.2026</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Фабрикант</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>06.03.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000002</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=2616712165226000005</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000002</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=2616712165226000005</t>
         </is>
       </c>
     </row>
@@ -1340,67 +1340,63 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Россия (федеральные/региональные)</t>
+          <t>Ростовская область</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Пешеходные переходы</t>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0362100008225000034</t>
+          <t>0358300436226000021</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Открытый конкурс (ЭОК)</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Урал" (Росавтодор)</t>
+          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Модульные пешеходные переходы на федеральных дорогах Свердловской области (Р-242 и др.)</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Поставка камер видеонаблюдения цилиндрических, 47 шт.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1410000</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Завершена 09.2025</t>
+          <t>Завершена 05.2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>РАД</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>03.09.2025</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0362100008225000034</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000021</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0362100008225000034</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000021</t>
         </is>
       </c>
     </row>
@@ -1410,67 +1406,65 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Россия (федеральные/региональные)</t>
+          <t>Ростовская область</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Пешеходные переходы</t>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000071</t>
+          <t>0358300315026000005</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Запрос ценовой информации</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Поволжье" (Росавтодор)</t>
+          <t>МУК "Централизованная библиотечная система" (г. Волгодонск)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Модульный надземный переход, Р-158, км 38+700, Нижегородская обл.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+          <t>Установка системы видеонаблюдения (52 камеры, 7 объектов)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1083270</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Завершена 06.2026</t>
+          <t>Завершена 24.07.2026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18.06.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zcp20/view/common-info.html?regNumber=0311100007226000071</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300315026000005</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000071</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300315026000005</t>
         </is>
       </c>
     </row>
@@ -1480,36 +1474,36 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Россия (федеральные/региональные)</t>
+          <t>Ростовская область</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Пешеходные переходы</t>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0351100008926000135</t>
+          <t>0358300436226000022</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Открытый конкурс (ЭОК)</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Сибирь" (Росавтодор)</t>
+          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Светофорный объект на пешеходном переходе (кнопка вызова), А-166 «Чуйский тракт», км 442+988</t>
+          <t>Мультимедийное ПО системы видеонаблюдения (лицензии)</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>7714064</v>
+        <v>2600000</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1518,27 +1512,27 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Приём заявок до 08.2026</t>
+          <t>Размещена 04.2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0351100008926000135</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000022</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0351100008926000135</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000022</t>
         </is>
       </c>
     </row>
@@ -1558,55 +1552,53 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0813500000126014575</t>
+          <t>0311100007226000004</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Запрос котировок</t>
+          <t>Открытый конкурс (ЭОК)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Управление «Шабердинское-Люкское» (Завьяловский МО, Удмуртия)</t>
+          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Установка светофора пешеходного перехода</t>
+          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 659+086, 661+289, 665+613), Чувашия</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>204004</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>138000000</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>138000000</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Приём заявок до 08.2026</t>
+          <t>Завершена 03.2026; победитель ООО «Вест»</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>Фабрикант</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>06.03.2026</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0813500000126014575</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000004</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0813500000126014575</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000004</t>
         </is>
       </c>
     </row>
@@ -1621,58 +1613,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение / фотовидеофиксация</t>
+          <t>Пешеходные переходы</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0118300013326000359</t>
+          <t>0311100007226000003</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Открытый конкурс (ЭОК)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>МБУ "АПК Безопасный город-ЕДДС" (г. Новороссийск)</t>
+          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Расширение функционала интеллектуальных модулей муниципальной системы видеонаблюдения</t>
+          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 626+954, 632+373, 634+365), Чувашия</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>19750333</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>19750333</v>
+        <v>138000000</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Контракт с ООО «Городские технологии» 20.04.2026</t>
+          <t>Завершена 03.2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>ТЭК-Торг</t>
+          <t>Фабрикант</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>06.03.2026</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0118300013326000359</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000003</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0118300013326000359</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000003</t>
         </is>
       </c>
     </row>
@@ -1687,31 +1681,31 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение / фотовидеофиксация</t>
+          <t>Пешеходные переходы</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0869200000226002435</t>
+          <t>0311100007226000002</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Открытый конкурс (ЭОК)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>ГКУ Челябинской области "Центр организации закупок"</t>
+          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Развитие АС фотовидеофиксации «Безопасный регион» у пешеходного перехода, ул. Горького / Правдухина, Челябинск</t>
+          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 622+767, 624+812, 635+693), Чувашия</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>5800000</v>
+        <v>138000000</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1720,27 +1714,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Аукцион 04.2026</t>
+          <t>Завершена 03.2026</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>ТЭК-Торг</t>
+          <t>Фабрикант</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>03.04.2026</t>
+          <t>06.03.2026</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0869200000226002435</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000002</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0869200000226002435</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000002</t>
         </is>
       </c>
     </row>
@@ -1755,65 +1749,475 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>Пешеходные переходы</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0362100008225000034</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Открытый конкурс (ЭОК)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>ФКУ "Упрдор Урал" (Росавтодор)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Модульные пешеходные переходы на федеральных дорогах Свердловской области (Р-242 и др.)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Завершена 09.2025</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>РАД</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>03.09.2025</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0362100008225000034</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0362100008225000034</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Россия (федеральные/региональные)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Пешеходные переходы</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0311100007226000071</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Запрос ценовой информации</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ФКУ "Упрдор Поволжье" (Росавтодор)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Модульный надземный переход, Р-158, км 38+700, Нижегородская обл.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Завершена 06.2026</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zcp20/view/common-info.html?regNumber=0311100007226000071</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000071</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Россия (федеральные/региональные)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Пешеходные переходы</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0351100008926000135</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Открытый конкурс (ЭОК)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ФКУ "Упрдор Сибирь" (Росавтодор)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Светофорный объект на пешеходном переходе (кнопка вызова), А-166 «Чуйский тракт», км 442+988</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>7714064</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Приём заявок до 08.2026</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0351100008926000135</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0351100008926000135</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Россия (федеральные/региональные)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Пешеходные переходы</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0813500000126014575</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Запрос котировок</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Управление «Шабердинское-Люкское» (Завьяловский МО, Удмуртия)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Установка светофора пешеходного перехода</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>204004</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Приём заявок до 08.2026</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0813500000126014575</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0813500000126014575</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Россия (федеральные/региональные)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0118300013326000359</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>МБУ "АПК Безопасный город-ЕДДС" (г. Новороссийск)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Расширение функционала интеллектуальных модулей муниципальной системы видеонаблюдения</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>19750333</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>19750333</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Контракт с ООО «Городские технологии» 20.04.2026</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0118300013326000359</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0118300013326000359</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Россия (федеральные/региональные)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0869200000226002435</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>ГКУ Челябинской области "Центр организации закупок"</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Развитие АС фотовидеофиксации «Безопасный регион» у пешеходного перехода, ул. Горького / Правдухина, Челябинск</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Аукцион 04.2026</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>03.04.2026</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0869200000226002435</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0869200000226002435</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Россия (федеральные/региональные)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>0311100007226000015</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Установка светофорных объектов на федеральных дорогах (в т.ч. пешеходные переходы), Чувашия</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>15441990</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Размещена 04.2026</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0311100007226000015</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000015</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:N26"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
@@ -1853,6 +2257,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Общая Тендеры РНД/реестр-лотов-44фз-пешеходные-переходы-видеонаблюдение.xlsx
+++ b/Общая Тендеры РНД/реестр-лотов-44фз-пешеходные-переходы-видеонаблюдение.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Реестр лотов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр лотов'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр лотов'!$A$1:$N$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -612,33 +612,35 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0158300010126000011</t>
+          <t>0358300439526000016</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Администрация Ремонтненского района РО</t>
+          <t>МБУ "Центр интеллектуальной транспортной системы" (г. Ростов-на-Дону, ИНН 6163132075)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Замена светофоров Т.7 (с солнечными светильниками) на пешеходных переходах МО дорог</t>
+          <t>Поставка, монтаж и пуско-наладка системы интеллектуального освещения пешеходного перехода, перекр. ул. Текучёва — пр. Ворошиловский</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1840797</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>984826</v>
+        <v>2708407</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Контракт заключён 10.08.2026</t>
+          <t>АКТИВНА — приём до 25.08.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -648,17 +650,17 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0158300010126000011</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0358300439526000016</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0158300010126000011</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300439526000016</t>
         </is>
       </c>
     </row>
@@ -678,55 +680,53 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0358300284526000154</t>
+          <t>0158300010126000011</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Запрос котировок</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>МКУ "ДИСОТИ" (дирекция транспортной инфраструктуры г. Ростова-на-Дону)</t>
+          <t>Администрация Ремонтненского района РО</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Переустройство пешеходных переходов на ул. Пушкинской (пер. Доломановский — пр. Театральный)</t>
+          <t>Замена светофоров Т.7 (с солнечными светильниками) на пешеходных переходах МО дорог</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8048700</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1840797</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>984826</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Приём завершён 15.07.2026</t>
+          <t>Контракт заключён 10.08.2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0358300284526000154</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0158300010126000011</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000154</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0158300010126000011</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0358300284526000125</t>
+          <t>0358300284526000154</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -761,38 +761,40 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Капремонт подземного перехода Кировский / Б. Садовая (ОКН, мозаика, видеонаблюдение)</t>
+          <t>Переустройство пешеходных переходов на ул. Пушкинской (пер. Доломановский — пр. Театральный)</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>48134495</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>46700000</v>
+        <v>8048700</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Повторный контракт 07.2026 (~46,7 млн ₽); ранее аукцион 05.2026</t>
+          <t>Приём завершён 15.07.2026</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27.05.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300284526000125</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0358300284526000154</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000125</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000154</t>
         </is>
       </c>
     </row>
@@ -812,7 +814,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0858300001826000064</t>
+          <t>0358300284526000125</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -822,45 +824,43 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Администрация г. Новошахтинска</t>
+          <t>МКУ "ДИСОТИ" (дирекция транспортной инфраструктуры г. Ростова-на-Дону)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Замена пешеходных светофорных устройств, пер. Водосборный — ул. Советской Конституции</t>
+          <t>Капремонт подземного перехода Кировский / Б. Садовая (ОКН, мозаика, видеонаблюдение)</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>248333</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>48134495</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46700000</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Завершена 06.2026</t>
+          <t>Повторный контракт 07.2026 (~46,7 млн ₽); ранее аукцион 05.2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16.06.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858300001826000064</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300284526000125</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858300001826000064</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000125</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение / фотовидеофиксация</t>
+          <t>Пешеходные переходы</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000003</t>
+          <t>0858300001826000064</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -890,43 +890,45 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
+          <t>Администрация г. Новошахтинска</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Услуги связи (VPN, передача данных с комплексов фиксации нарушений ПДД на территории РО)</t>
+          <t>Замена пешеходных светофорных устройств, пер. Водосборный — ул. Советской Конституции</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10298296</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>10298296</v>
+        <v>248333</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Контракт с ПАО «МегаФон» 16.02.2026</t>
+          <t>Завершена 06.2026</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>16.06.2026</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000003</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858300001826000064</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000003</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858300001826000064</t>
         </is>
       </c>
     </row>
@@ -946,12 +948,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000015</t>
+          <t>0858200000426000003</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Запрос котировок</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -961,20 +963,18 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>VPN и передача данных с комплексов фиксации ПДД в г. Ростов-на-Дону до центрального сервера</t>
+          <t>Услуги связи (VPN, передача данных с комплексов фиксации нарушений ПДД на территории РО)</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4533530</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10298296</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>10298296</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Приём завершён 14.08.2026</t>
+          <t>Контракт с ПАО «МегаФон» 16.02.2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000015</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000003</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000015</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000003</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000016</t>
+          <t>0858200000426000015</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Страхование имущества 71 комплекса фотовидеофиксации нарушений ПДД</t>
+          <t>VPN и передача данных с комплексов фиксации ПДД в г. Ростов-на-Дону до центрального сервера</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1439029</v>
+        <v>4533530</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Приём завершён 18.08.2026</t>
+          <t>Приём завершён 14.08.2026</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000016</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000015</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000016</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000015</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000013</t>
+          <t>0858200000426000016</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Запрос котировок</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1097,38 +1097,40 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Модернизация 8 комплексов «ЛОБАЧЕВСКИЙ» (доп. виды нарушений ПДД)</t>
+          <t>Страхование имущества 71 комплекса фотовидеофиксации нарушений ПДД</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2360000</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>2360000</v>
+        <v>1439029</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Контракт с ИП Батычко 29.05.2026</t>
+          <t>Приём завершён 18.08.2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25.05.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000013</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000016</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000013</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000016</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1150,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000014</t>
+          <t>0858200000426000013</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1163,18 +1165,18 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Модернизация комплексов «СКИП-Траффик ПДД» (доп. виды нарушений), 9 комплексов</t>
+          <t>Модернизация 8 комплексов «ЛОБАЧЕВСКИЙ» (доп. виды нарушений ПДД)</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2655000</v>
+        <v>2360000</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2655000</v>
+        <v>2360000</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Контракт 22.06.2026</t>
+          <t>Контракт с ИП Батычко 29.05.2026</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1184,17 +1186,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16.06.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000014</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000013</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000014</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000013</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1216,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0858200000426000006</t>
+          <t>0858200000426000014</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1229,22 +1231,18 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ИБ ГИС «Интеллектуальная транспортная система Ростовской области» (ОКИИ)</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Модернизация комплексов «СКИП-Траффик ПДД» (доп. виды нарушений), 9 комплексов</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>2655000</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>2655000</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Завершена 04.2026</t>
+          <t>Контракт 22.06.2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1254,17 +1252,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>16.06.2026</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000006</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000014</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000006</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000014</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2616712165226000005</t>
+          <t>0858200000426000006</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1299,38 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Поставка электроэнергии для комплексов фиксации</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>3500000</v>
+          <t>ИБ ГИС «Интеллектуальная транспортная система Ростовской области» (ОКИИ)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Контракт 04.2026</t>
+          <t>Завершена 04.2026</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>07.04.2026</t>
+          <t>06.04.2026</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=2616712165226000005</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000006</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=2616712165226000005</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000006</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1352,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0358300436226000021</t>
+          <t>2616712165226000005</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1360,43 +1362,43 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
+          <t>ГКУ РО "Центр безопасности дорожного движения"</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Поставка камер видеонаблюдения цилиндрических, 47 шт.</t>
+          <t>Поставка электроэнергии для комплексов фиксации</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1410000</v>
+        <v>3500000</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1410000</v>
+        <v>3500000</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Завершена 05.2026</t>
+          <t>Контракт 04.2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000021</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=2616712165226000005</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000021</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=2616712165226000005</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1418,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0358300315026000005</t>
+          <t>0358300436226000021</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1426,45 +1428,43 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>МУК "Централизованная библиотечная система" (г. Волгодонск)</t>
+          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Установка системы видеонаблюдения (52 камеры, 7 объектов)</t>
+          <t>Поставка камер видеонаблюдения цилиндрических, 47 шт.</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1083270</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1410000</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1410000</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Завершена 24.07.2026</t>
+          <t>Завершена 05.2026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300315026000005</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000021</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300315026000005</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000021</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0358300436226000022</t>
+          <t>0358300315026000005</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1494,16 +1494,16 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
+          <t>МУК "Централизованная библиотечная система" (г. Волгодонск)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Мультимедийное ПО системы видеонаблюдения (лицензии)</t>
+          <t>Установка системы видеонаблюдения (52 камеры, 7 объектов)</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2600000</v>
+        <v>1083270</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1512,27 +1512,27 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Размещена 04.2026</t>
+          <t>Завершена 24.07.2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000022</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300315026000005</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000022</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300315026000005</t>
         </is>
       </c>
     </row>
@@ -1542,63 +1542,65 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Россия (федеральные/региональные)</t>
+          <t>Ростовская область</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Пешеходные переходы</t>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000004</t>
+          <t>0358300436226000022</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Открытый конкурс (ЭОК)</t>
+          <t>Электронный аукцион</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
+          <t>МКУ "Защита и безопасность" (г. Ростов-на-Дону)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 659+086, 661+289, 665+613), Чувашия</t>
+          <t>Мультимедийное ПО системы видеонаблюдения (лицензии)</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>138000000</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>138000000</v>
+        <v>2600000</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Завершена 03.2026; победитель ООО «Вест»</t>
+          <t>Размещена 04.2026</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Фабрикант</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>06.03.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000004</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000022</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000004</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000022</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1620,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000003</t>
+          <t>0311100007226000004</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1633,20 +1635,18 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 626+954, 632+373, 634+365), Чувашия</t>
+          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 659+086, 661+289, 665+613), Чувашия</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
         <v>138000000</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>138000000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Завершена 03.2026</t>
+          <t>Завершена 03.2026; победитель ООО «Вест»</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000003</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000004</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000003</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000004</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000002</t>
+          <t>0311100007226000003</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 622+767, 624+812, 635+693), Чувашия</t>
+          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 626+954, 632+373, 634+365), Чувашия</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000002</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000003</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000002</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000003</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0362100008225000034</t>
+          <t>0311100007226000002</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1764,47 +1764,45 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Урал" (Росавтодор)</t>
+          <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Модульные пешеходные переходы на федеральных дорогах Свердловской области (Р-242 и др.)</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+          <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 622+767, 624+812, 635+693), Чувашия</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Завершена 09.2025</t>
+          <t>Завершена 03.2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>РАД</t>
+          <t>Фабрикант</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>03.09.2025</t>
+          <t>06.03.2026</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0362100008225000034</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000002</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0362100008225000034</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000002</t>
         </is>
       </c>
     </row>
@@ -1824,22 +1822,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0311100007226000071</t>
+          <t>0362100008225000034</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Запрос ценовой информации</t>
+          <t>Открытый конкурс (ЭОК)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Поволжье" (Росавтодор)</t>
+          <t>ФКУ "Упрдор Урал" (Росавтодор)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Модульный надземный переход, Р-158, км 38+700, Нижегородская обл.</t>
+          <t>Модульные пешеходные переходы на федеральных дорогах Свердловской области (Р-242 и др.)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1854,27 +1852,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Завершена 06.2026</t>
+          <t>Завершена 09.2025</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>РАД</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18.06.2026</t>
+          <t>03.09.2025</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zcp20/view/common-info.html?regNumber=0311100007226000071</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0362100008225000034</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000071</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0362100008225000034</t>
         </is>
       </c>
     </row>
@@ -1894,26 +1892,28 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0351100008926000135</t>
+          <t>0311100007226000071</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Открытый конкурс (ЭОК)</t>
+          <t>Запрос ценовой информации</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>ФКУ "Упрдор Сибирь" (Росавтодор)</t>
+          <t>ФКУ "Упрдор Поволжье" (Росавтодор)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Светофорный объект на пешеходном переходе (кнопка вызова), А-166 «Чуйский тракт», км 442+988</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>7714064</v>
+          <t>Модульный надземный переход, Р-158, км 38+700, Нижегородская обл.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Приём заявок до 08.2026</t>
+          <t>Завершена 06.2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>18.06.2026</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0351100008926000135</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zcp20/view/common-info.html?regNumber=0311100007226000071</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0351100008926000135</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000071</t>
         </is>
       </c>
     </row>
@@ -1962,26 +1962,26 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0813500000126014575</t>
+          <t>0351100008926000135</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Запрос котировок</t>
+          <t>Открытый конкурс (ЭОК)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Управление «Шабердинское-Люкское» (Завьяловский МО, Удмуртия)</t>
+          <t>ФКУ "Упрдор Сибирь" (Росавтодор)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Установка светофора пешеходного перехода</t>
+          <t>Светофорный объект на пешеходном переходе (кнопка вызова), А-166 «Чуйский тракт», км 442+988</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>204004</v>
+        <v>7714064</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0813500000126014575</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0351100008926000135</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0813500000126014575</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0351100008926000135</t>
         </is>
       </c>
     </row>
@@ -2025,58 +2025,60 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение / фотовидеофиксация</t>
+          <t>Пешеходные переходы</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0118300013326000359</t>
+          <t>0813500000126014575</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Электронный аукцион</t>
+          <t>Запрос котировок</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>МБУ "АПК Безопасный город-ЕДДС" (г. Новороссийск)</t>
+          <t>Управление «Шабердинское-Люкское» (Завьяловский МО, Удмуртия)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Расширение функционала интеллектуальных модулей муниципальной системы видеонаблюдения</t>
+          <t>Установка светофора пешеходного перехода</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>19750333</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>19750333</v>
+        <v>204004</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Контракт с ООО «Городские технологии» 20.04.2026</t>
+          <t>Приём заявок до 08.2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>ТЭК-Торг</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0118300013326000359</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0813500000126014575</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0118300013326000359</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0813500000126014575</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2098,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0869200000226002435</t>
+          <t>0118300013326000359</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2106,25 +2108,23 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ГКУ Челябинской области "Центр организации закупок"</t>
+          <t>МБУ "АПК Безопасный город-ЕДДС" (г. Новороссийск)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Развитие АС фотовидеофиксации «Безопасный регион» у пешеходного перехода, ул. Горького / Правдухина, Челябинск</t>
+          <t>Расширение функционала интеллектуальных модулей муниципальной системы видеонаблюдения</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>19750333</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>19750333</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Аукцион 04.2026</t>
+          <t>Контракт с ООО «Городские технологии» 20.04.2026</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2134,17 +2134,17 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>03.04.2026</t>
+          <t>06.04.2026</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0869200000226002435</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0118300013326000359</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0869200000226002435</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0118300013326000359</t>
         </is>
       </c>
     </row>
@@ -2164,60 +2164,128 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>0869200000226002435</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>ГКУ Челябинской области "Центр организации закупок"</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Развитие АС фотовидеофиксации «Безопасный регион» у пешеходного перехода, ул. Горького / Правдухина, Челябинск</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Аукцион 04.2026</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>03.04.2026</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0869200000226002435</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0869200000226002435</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Россия (федеральные/региональные)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение / фотовидеофиксация</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>0311100007226000015</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>ФКУ "Упрдор Волга" (Росавтодор)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Установка светофорных объектов на федеральных дорогах (в т.ч. пешеходные переходы), Чувашия</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>15441990</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Размещена 04.2026</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0311100007226000015</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000015</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N26"/>
+  <autoFilter ref="A1:N27"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
@@ -2269,6 +2337,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Общая Тендеры РНД/реестр-лотов-44фз-пешеходные-переходы-видеонаблюдение.xlsx
+++ b/Общая Тендеры РНД/реестр-лотов-44фз-пешеходные-переходы-видеонаблюдение.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Реестр лотов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр лотов'!$A$1:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр лотов'!$A$1:$O$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -447,13 +447,14 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,35 +495,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Расширенное описание</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>НМЦК, ₽</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена контракта, ₽</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ЭТП</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Окончание заявок</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Ссылка ЕИС</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Поиск в ЕИС</t>
         </is>
@@ -562,35 +568,40 @@
           <t>Обустройство пешеходных переходов ограждениями и светофорами типа Т-7</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион. ОКПД2 42.11.20.190. Обустройство пешеходных переходов ограждениями и светофорами типа Т-7 в г. Сальск. Преимущество СМП (ст. 30). Заказчик: администрация Сальского г.п., ИНН 6153023616, ул. Ленина, 21. Опубликовано 17.08.2026; изменение извещения 17.08.2026.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>1716251</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>АКТИВНА — приём до 21.08.2026 09:00 МСК</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>21.08.2026</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0158300033626000068</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0158300033626000068</t>
         </is>
@@ -630,35 +641,40 @@
           <t>Поставка, монтаж и пуско-наладка системы интеллектуального освещения пешеходного перехода, перекр. ул. Текучёва — пр. Ворошиловский</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, запрос котировок. РТС-тендер. Перекрёсток ул. Текучёва — пр. Ворошиловский, Ростов-на-Дону. Состав: светодиодные прожекторы (27.40.33.130), ПО (58.29.2), устройства дорожной сигнализации (27.90.7), антенны, монтаж и пуско-наладка (43.21.10.290). Заказчик МБУ «ЦИТС», ИНН 6163132075, ул. Социалистическая, 135; контакт pev@its-rnd.ru, 7-863-2277814. Опубликовано 15.08.2026.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>2708407</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>АКТИВНА — приём до 25.08.2026 08:00 МСК</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>25.08.2026</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0358300439526000016</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300439526000016</t>
         </is>
@@ -698,33 +714,38 @@
           <t>Замена светофоров Т.7 (с солнечными светильниками) на пешеходных переходах МО дорог</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, РТС-тендер. Преимущество СМП. Замена светофоров Т.7 с солнечными светильниками на пешеходных переходах муниципальных дорог Ремонтненского района. НМЦК 1,84 млн ₽; контракт 984 826 ₽ (−47%). Исполнение до 31.12.2026.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>1840797</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>984826</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Контракт заключён 10.08.2026</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>27.07.2026</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0158300010126000011</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0158300010126000011</t>
         </is>
@@ -764,35 +785,40 @@
           <t>Переустройство пешеходных переходов на ул. Пушкинской (пер. Доломановский — пр. Театральный)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, запрос котировок. КТРУ 42.11.20.200 — ремонт автомобильных дорог. Переустройство пешеходных переходов на ул. Пушкинской между пер. Доломановский и пр. Театральный. Заказчик МКУ «ДИСОТИ», ИНН 6164294858. Размещено 08.07.2026.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>8048700</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Приём завершён 15.07.2026</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>15.07.2026</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0358300284526000154</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000154</t>
         </is>
@@ -832,33 +858,38 @@
           <t>Капремонт подземного перехода Кировский / Б. Садовая (ОКН, мозаика, видеонаблюдение)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, Сбербанк-АСТ. Капремонт подземного перехода «Кировский» / Б. Садовая — объект культурного наследия (мозаика). В составе работ: освещение, вентиляция, видеонаблюдение. Программа по 4 переходам в центре Ростова — ~440 млн ₽ (2025). Контракт ~46,7 млн ₽.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>48134495</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>46700000</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Повторный контракт 07.2026 (~46,7 млн ₽); ранее аукцион 05.2026</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Сбербанк-АСТ</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300284526000125</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300284526000125</t>
         </is>
@@ -898,35 +929,40 @@
           <t>Замена пешеходных светофорных устройств, пер. Водосборный — ул. Советской Конституции</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, Росэлторг. Замена пешеходных светофорных устройств на пер. Водосборный — ул. Советской Конституции, г. Новошахтинск. Обеспечение контракта 5%. НМЦК 248 333 ₽.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>248333</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Завершена 06.2026</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Росэлторг</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>16.06.2026</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858300001826000064</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858300001826000064</t>
         </is>
@@ -966,33 +1002,38 @@
           <t>Услуги связи (VPN, передача данных с комплексов фиксации нарушений ПДД на территории РО)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>10298296</v>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, РТС-тендер. VPN и передача данных со стационарных комплексов фиксации ПДД по всей Ростовской области до центрального сервера. Заказчик ГКУ РО «Центр БДД», ИНН 6167121652. Контракт с ПАО «МегаФон» 16.02.2026 на 10,30 млн ₽.</t>
+        </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>10298296</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="n">
+        <v>10298296</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Контракт с ПАО «МегаФон» 16.02.2026</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>03.02.2026</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000003</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000003</t>
         </is>
@@ -1032,35 +1073,40 @@
           <t>VPN и передача данных с комплексов фиксации ПДД в г. Ростов-на-Дону до центрального сервера</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, запрос котировок, РТС-тендер. VPN и передача данных с комплексов фиксации ПДД только в границах улично-дорожной сети г. Ростова-на-Дону. Отдельный лот от февральского VPN по всей РО (0858200000426000003). Приём заявок 07–14.08.2026.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>4533530</v>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Приём завершён 14.08.2026</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>14.08.2026</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000015</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000015</t>
         </is>
@@ -1100,35 +1146,40 @@
           <t>Страхование имущества 71 комплекса фотовидеофиксации нарушений ПДД</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион. Страхование имущества 71 комплекса фотовидеофиксации (Кордон-М2, Кордон.Про М, ЛОБАЧЕВСКИЙ, СКИП-Траффик ПДД). Стоимость имущества ~179 млн ₽. Риски: кража, вандализм, БПЛА, стихийные бедствия. Размещено 10.08.2026.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>1439029</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Приём завершён 18.08.2026</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>18.08.2026</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000016</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000016</t>
         </is>
@@ -1168,33 +1219,38 @@
           <t>Модернизация 8 комплексов «ЛОБАЧЕВСКИЙ» (доп. виды нарушений ПДД)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>2360000</v>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, запрос котировок, РТС-тендер. ОКПД2 33.13.13.000. Модернизация 8 комплексов «ЛОБАЧЕВСКИЙ» для фиксации дополнительных видов нарушений ПДД. Контракт с ИП Батычко А.В. 29.05.2026 на 2,36 млн ₽; исполнение до 31.07.2026.</t>
+        </is>
       </c>
       <c r="I11" s="2" t="n">
         <v>2360000</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Контракт с ИП Батычко 29.05.2026</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>25.05.2026</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000013</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000013</t>
         </is>
@@ -1234,33 +1290,38 @@
           <t>Модернизация комплексов «СКИП-Траффик ПДД» (доп. виды нарушений), 9 комплексов</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>2655000</v>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, запрос котировок, РТС-тендер. Модернизация 9 комплексов «СКИП-Траффик ПДД» — расширение перечня фиксируемых нарушений. Контракт 22.06.2026 на 2,655 млн ₽.</t>
+        </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>2655000</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="n">
+        <v>2655000</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Контракт 22.06.2026</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>16.06.2026</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0858200000426000014</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000014</t>
         </is>
@@ -1302,35 +1363,40 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>44-ФЗ, электронный аукцион, РТС-тендер. Информационная безопасность ГИС «Интеллектуальная транспортная система Ростовской области» (объект КИИ). Заказчик ГКУ РО «Центр БДД». Завершена 04.2026.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Завершена 04.2026</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0858200000426000006</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0858200000426000006</t>
         </is>
@@ -1370,33 +1436,38 @@
           <t>Поставка электроэнергии для комплексов фиксации</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>3500000</v>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион. Поставка электроэнергии для комплексов автоматической фиксации нарушений ПДД на территории РО. Рекуррентная закупка ЦБДД. Контракт 04.2026 на 3,50 млн ₽.</t>
+        </is>
       </c>
       <c r="I14" s="2" t="n">
         <v>3500000</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Контракт 04.2026</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=2616712165226000005</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=2616712165226000005</t>
         </is>
@@ -1436,33 +1507,38 @@
           <t>Поставка камер видеонаблюдения цилиндрических, 47 шт.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>1410000</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, Сбербанк-АСТ. Поставка 47 цилиндрических IP-камер для муниципальной системы видеонаблюдения. Заказчик МКУ «Защита и безопасность», г. Ростов-на-Дону. Ориентир по спецификации (Hikvision): DS-2CD2043G2-IU (цилиндрические), DS-2DE5432IW-AE (PTZ), NVR DS-7608NXI-K2/8P, PoE-коммутатор DH-CS4010-8ET2GT-110, HDD ST2000VX017; ориентир СМР ~155 040 ₽.</t>
+        </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>1410000</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Завершена 05.2026</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Сбербанк-АСТ</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>06.05.2026</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000021</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000021</t>
         </is>
@@ -1502,35 +1578,40 @@
           <t>Установка системы видеонаблюдения (52 камеры, 7 объектов)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, РТС-тендер. Установка системы видеонаблюдения на 7 объектах библиотек г. Волгодонска: 52 камеры (15+37), 8 видеорегистраторов, 8 коммутаторов, 8 ИБП, 8 накопителей. Заказчик МУК «ЦБС», ул. Ленина, 75. НМЦК 1,08 млн ₽.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>1083270</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Завершена 24.07.2026</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>24.07.2026</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300315026000005</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300315026000005</t>
         </is>
@@ -1570,35 +1651,40 @@
           <t>Мультимедийное ПО системы видеонаблюдения (лицензии)</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, Сбербанк-АСТ. Мультимедийное ПО системы видеонаблюдения (лицензии) для муниципальной системы Ростова-на-Дону. Заказчик МКУ «Защита и безопасность». Связанный лот на камеры — 0358300436226000021.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>2600000</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Размещена 04.2026</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Сбербанк-АСТ</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0358300436226000022</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0358300436226000022</t>
         </is>
@@ -1638,33 +1724,38 @@
           <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 659+086, 661+289, 665+613), Чувашия</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>138000000</v>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, открытый конкурс (ЭОК), Фабрикант. Модульные надземные пешеходные переходы на федеральной трассе М-7 «Волга», 3 точки (км 659+086, 661+289, 665+613), Чувашия. Заказчик ФКУ «Упрдор Волга» (Росавтодор). НМЦК 138 млн ₽; контракт с ООО «Вест».</t>
+        </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>138000000</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Завершена 03.2026; победитель ООО «Вест»</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Фабрикант</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>06.03.2026</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000004</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000004</t>
         </is>
@@ -1704,35 +1795,40 @@
           <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 626+954, 632+373, 634+365), Чувашия</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, открытый конкурс (ЭОК), Фабрикант. Модульные надземные переходы на М-7 «Волга», 3 точки (км 626+954, 632+373, 634+365), Чувашия. Заказчик ФКУ «Упрдор Волга». НМЦК 138 млн ₽. Завершена 03.2026.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>138000000</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Завершена 03.2026</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Фабрикант</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>06.03.2026</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000003</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000003</t>
         </is>
@@ -1772,35 +1868,40 @@
           <t>Модульные надземные переходы, М-7 «Волга», 3 точки (км 622+767, 624+812, 635+693), Чувашия</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, открытый конкурс (ЭОК), Фабрикант. Модульные надземные переходы на М-7 «Волга», 3 точки (км 622+767, 624+812, 635+693), Чувашия. Заказчик ФКУ «Упрдор Волга». НМЦК 138 млн ₽. Завершена 03.2026.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>138000000</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Завершена 03.2026</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Фабрикант</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>06.03.2026</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0311100007226000002</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000002</t>
         </is>
@@ -1842,35 +1943,40 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>44-ФЗ, открытый конкурс (ЭОК), РАД. Модульные пешеходные переходы на федеральных дорогах Свердловской области (Р-242 и др.). Заказчик ФКУ «Упрдор Урал» (Росавтодор). Завершена 09.2025.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Завершена 09.2025</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>РАД</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>03.09.2025</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0362100008225000034</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0362100008225000034</t>
         </is>
@@ -1912,35 +2018,40 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>44-ФЗ, запрос ценовой информации. Модульный надземный пешеходный переход на федеральной дороге Р-158, км 38+700, Нижегородская обл. Заказчик ФКУ «Упрдор Поволжье». Завершена 06.2026.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Завершена 06.2026</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>18.06.2026</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zcp20/view/common-info.html?regNumber=0311100007226000071</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000071</t>
         </is>
@@ -1980,35 +2091,40 @@
           <t>Светофорный объект на пешеходном переходе (кнопка вызова), А-166 «Чуйский тракт», км 442+988</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, открытый конкурс (ЭОК). Светофорный объект на пешеходном переходе с кнопкой вызова, А-166 «Чуйский тракт», км 442+988. Заказчик ФКУ «Упрдор Сибирь». НМЦК 7,71 млн ₽. Приём заявок до 11.08.2026.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>7714064</v>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Приём заявок до 08.2026</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>11.08.2026</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ok20/view/common-info.html?regNumber=0351100008926000135</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0351100008926000135</t>
         </is>
@@ -2048,35 +2164,40 @@
           <t>Установка светофора пешеходного перехода</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, запрос котировок. Установка светофора пешеходного перехода в Завьяловском МО, Удмуртия. Заказчик Управление «Шабердинское-Люкское». НМЦК 204 004 ₽. Приём до 04.08.2026.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>204004</v>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Приём заявок до 08.2026</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>04.08.2026</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0813500000126014575</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0813500000126014575</t>
         </is>
@@ -2116,33 +2237,38 @@
           <t>Расширение функционала интеллектуальных модулей муниципальной системы видеонаблюдения</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>19750333</v>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, ТЭК-Торг. Расширение функционала интеллектуальных модулей муниципальной системы «Безопасный город-ЕДДС», г. Новороссийск. НМЦК 19,75 млн ₽; контракт с ООО «Городские технологии» 20.04.2026.</t>
+        </is>
       </c>
       <c r="I25" s="2" t="n">
         <v>19750333</v>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="n">
+        <v>19750333</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Контракт с ООО «Городские технологии» 20.04.2026</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>ТЭК-Торг</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0118300013326000359</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0118300013326000359</t>
         </is>
@@ -2182,35 +2308,40 @@
           <t>Развитие АС фотовидеофиксации «Безопасный регион» у пешеходного перехода, ул. Горького / Правдухина, Челябинск</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион, ТЭК-Торг. Развитие АС фотовидеофиксации «Безопасный регион» у пешеходного перехода на перекрёстке ул. Горького / Правдухина, Челябинск. Заказчик ГКУ Челябинской области «ЦОЗ». НМЦК 5,80 млн ₽.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>5800000</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Аукцион 04.2026</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>ТЭК-Торг</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>03.04.2026</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0869200000226002435</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0869200000226002435</t>
         </is>
@@ -2250,95 +2381,100 @@
           <t>Установка светофорных объектов на федеральных дорогах (в т.ч. пешеходные переходы), Чувашия</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>44-ФЗ, электронный аукцион. Установка светофорных объектов на федеральных дорогах Чувашии, в т.ч. на пешеходных переходах. Заказчик ФКУ «Упрдор Волга». НМЦК 15,44 млн ₽. Размещена 04.2026.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
         <v>15441990</v>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Размещена 04.2026</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/ea20/view/common-info.html?regNumber=0311100007226000015</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0311100007226000015</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N27"/>
+  <autoFilter ref="A1:O27"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
